--- a/artfynd/A 30580-2022 artfynd.xlsx
+++ b/artfynd/A 30580-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130040065</v>
       </c>
       <c r="B2" t="n">
-        <v>96143</v>
+        <v>96144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130040064</v>
       </c>
       <c r="B3" t="n">
-        <v>96239</v>
+        <v>96240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130040059</v>
       </c>
       <c r="B4" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130040063</v>
       </c>
       <c r="B5" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130040057</v>
       </c>
       <c r="B6" t="n">
-        <v>96143</v>
+        <v>96144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130040058</v>
       </c>
       <c r="B7" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30580-2022 artfynd.xlsx
+++ b/artfynd/A 30580-2022 artfynd.xlsx
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130040059</v>
+        <v>130040063</v>
       </c>
       <c r="B4" t="n">
-        <v>91570</v>
+        <v>97044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684666</v>
+        <v>684709</v>
       </c>
       <c r="R4" t="n">
-        <v>6650835</v>
+        <v>6650804</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130040063</v>
+        <v>130040059</v>
       </c>
       <c r="B5" t="n">
-        <v>97044</v>
+        <v>91570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684709</v>
+        <v>684666</v>
       </c>
       <c r="R5" t="n">
-        <v>6650804</v>
+        <v>6650835</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 30580-2022 artfynd.xlsx
+++ b/artfynd/A 30580-2022 artfynd.xlsx
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130040063</v>
+        <v>130040059</v>
       </c>
       <c r="B4" t="n">
-        <v>97044</v>
+        <v>91570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684709</v>
+        <v>684666</v>
       </c>
       <c r="R4" t="n">
-        <v>6650804</v>
+        <v>6650835</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130040059</v>
+        <v>130040063</v>
       </c>
       <c r="B5" t="n">
-        <v>91570</v>
+        <v>97044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684666</v>
+        <v>684709</v>
       </c>
       <c r="R5" t="n">
-        <v>6650835</v>
+        <v>6650804</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 30580-2022 artfynd.xlsx
+++ b/artfynd/A 30580-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130040065</v>
       </c>
       <c r="B2" t="n">
-        <v>96144</v>
+        <v>96161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130040064</v>
       </c>
       <c r="B3" t="n">
-        <v>96240</v>
+        <v>96257</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130040059</v>
+        <v>130040063</v>
       </c>
       <c r="B4" t="n">
-        <v>91570</v>
+        <v>97061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684666</v>
+        <v>684709</v>
       </c>
       <c r="R4" t="n">
-        <v>6650835</v>
+        <v>6650804</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130040063</v>
+        <v>130040059</v>
       </c>
       <c r="B5" t="n">
-        <v>97044</v>
+        <v>91587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684709</v>
+        <v>684666</v>
       </c>
       <c r="R5" t="n">
-        <v>6650804</v>
+        <v>6650835</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
         <v>130040057</v>
       </c>
       <c r="B6" t="n">
-        <v>96144</v>
+        <v>96161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130040058</v>
       </c>
       <c r="B7" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30580-2022 artfynd.xlsx
+++ b/artfynd/A 30580-2022 artfynd.xlsx
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130040063</v>
+        <v>130040059</v>
       </c>
       <c r="B4" t="n">
-        <v>97077</v>
+        <v>91603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684709</v>
+        <v>684666</v>
       </c>
       <c r="R4" t="n">
-        <v>6650804</v>
+        <v>6650835</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130040059</v>
+        <v>130040063</v>
       </c>
       <c r="B5" t="n">
-        <v>91603</v>
+        <v>97077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684666</v>
+        <v>684709</v>
       </c>
       <c r="R5" t="n">
-        <v>6650835</v>
+        <v>6650804</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 30580-2022 artfynd.xlsx
+++ b/artfynd/A 30580-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130040065</v>
       </c>
       <c r="B2" t="n">
-        <v>96177</v>
+        <v>96179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130040064</v>
       </c>
       <c r="B3" t="n">
-        <v>96273</v>
+        <v>96275</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130040059</v>
       </c>
       <c r="B4" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130040063</v>
       </c>
       <c r="B5" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130040057</v>
       </c>
       <c r="B6" t="n">
-        <v>96177</v>
+        <v>96179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130040058</v>
       </c>
       <c r="B7" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30580-2022 artfynd.xlsx
+++ b/artfynd/A 30580-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130040065</v>
       </c>
       <c r="B2" t="n">
-        <v>96179</v>
+        <v>96266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130040064</v>
       </c>
       <c r="B3" t="n">
-        <v>96275</v>
+        <v>96362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130040059</v>
+        <v>130040063</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
+        <v>97166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684666</v>
+        <v>684709</v>
       </c>
       <c r="R4" t="n">
-        <v>6650835</v>
+        <v>6650804</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130040063</v>
+        <v>130040059</v>
       </c>
       <c r="B5" t="n">
-        <v>97079</v>
+        <v>91692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684709</v>
+        <v>684666</v>
       </c>
       <c r="R5" t="n">
-        <v>6650804</v>
+        <v>6650835</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
         <v>130040057</v>
       </c>
       <c r="B6" t="n">
-        <v>96179</v>
+        <v>96266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130040058</v>
       </c>
       <c r="B7" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30580-2022 artfynd.xlsx
+++ b/artfynd/A 30580-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130040065</v>
+        <v>130040063</v>
       </c>
       <c r="B2" t="n">
-        <v>96266</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>684871</v>
+        <v>684709</v>
       </c>
       <c r="R2" t="n">
-        <v>6650767</v>
+        <v>6650804</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130040064</v>
+        <v>130040060</v>
       </c>
       <c r="B3" t="n">
-        <v>96362</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>684756</v>
+        <v>684644</v>
       </c>
       <c r="R3" t="n">
-        <v>6650832</v>
+        <v>6650821</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>björkstubbe</t>
+          <t>låga av obestämt trädslag</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130040063</v>
+        <v>130040064</v>
       </c>
       <c r="B4" t="n">
-        <v>97166</v>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684709</v>
+        <v>684756</v>
       </c>
       <c r="R4" t="n">
-        <v>6650804</v>
+        <v>6650832</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>björkstubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130040059</v>
+        <v>130040057</v>
       </c>
       <c r="B5" t="n">
-        <v>91692</v>
+        <v>96458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684666</v>
+        <v>684686</v>
       </c>
       <c r="R5" t="n">
-        <v>6650835</v>
+        <v>6650828</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>granstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130040057</v>
+        <v>130040061</v>
       </c>
       <c r="B6" t="n">
-        <v>96266</v>
+        <v>96458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>684686</v>
+        <v>684645</v>
       </c>
       <c r="R6" t="n">
-        <v>6650828</v>
+        <v>6650811</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>granstubbe</t>
+          <t>låga av obestämt trädslag</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,30 +1235,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130040058</v>
+        <v>130040065</v>
       </c>
       <c r="B7" t="n">
-        <v>91748</v>
+        <v>96458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1266,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684668</v>
+        <v>684871</v>
       </c>
       <c r="R7" t="n">
-        <v>6650834</v>
+        <v>6650767</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,6 +1344,118 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130040059</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rimsarmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>684666</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6650835</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Bergvik Skog</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>äldre granskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
